--- a/artfynd/A 30756-2025 artfynd.xlsx
+++ b/artfynd/A 30756-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56495700</v>
+        <v>56495699</v>
       </c>
       <c r="B2" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551591.243272912</v>
+        <v>551653</v>
       </c>
       <c r="R2" t="n">
-        <v>7152389.101311401</v>
+        <v>7152348</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2015-08-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-08-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +767,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>1 substratenheter # Sälg</t>
+          <t>1 substratenheter # Död gran</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,6 +782,120 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>56495700</v>
+      </c>
+      <c r="B3" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kojmyran, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>551591</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7152389</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2015-08-23</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2015-08-23</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Lövrik granskog</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Sälg</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Niina Sallmén, Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
